--- a/data/chains_snippet.xlsx
+++ b/data/chains_snippet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j7tran\GitHub\2026_anziam_vic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCDD6C2-26A8-4A00-92C2-5F5690A1424F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C1BAE9-FF21-49C0-9FEF-7A4DE2E26C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Database (2015)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Database (2015)'!$A$1:$R$563</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Database (2015)'!$A$1:$R$525</definedName>
   </definedNames>
   <calcPr calcId="140000" concurrentCalc="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="38">
   <si>
     <t>Round</t>
   </si>
@@ -111,9 +111,6 @@
     <t>AM</t>
   </si>
   <si>
-    <t>C.Yarran</t>
-  </si>
-  <si>
     <t>handball</t>
   </si>
   <si>
@@ -126,13 +123,7 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>Behind</t>
-  </si>
-  <si>
     <t>T.Menzel</t>
-  </si>
-  <si>
-    <t>T.Bell</t>
   </si>
   <si>
     <t>Kick In</t>
@@ -566,7 +557,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultColWidth="65.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12.25" style="2" bestFit="1" customWidth="1"/>
@@ -653,52 +644,52 @@
         <v>19</v>
       </c>
       <c r="C2" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="2">
+        <v>56</v>
+      </c>
+      <c r="K2" s="2">
+        <v>-24</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="2">
         <v>31</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="N2" s="2">
+        <v>-60</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="2">
-        <v>2</v>
-      </c>
-      <c r="K2" s="2">
-        <v>-4</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="2">
-        <v>10</v>
-      </c>
-      <c r="N2" s="2">
-        <v>-8</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="P2" s="2">
         <v>1</v>
       </c>
       <c r="Q2" s="2">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="R2" s="2">
-        <v>229</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -709,40 +700,40 @@
         <v>19</v>
       </c>
       <c r="C3" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="2">
         <v>31</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="2">
-        <v>10</v>
-      </c>
       <c r="K3" s="2">
-        <v>-8</v>
+        <v>-60</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M3" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3" s="2">
-        <v>1</v>
+        <v>-56</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>22</v>
@@ -751,10 +742,10 @@
         <v>1</v>
       </c>
       <c r="Q3" s="2">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="R3" s="2">
-        <v>231</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -765,7 +756,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>21</v>
@@ -774,31 +765,31 @@
         <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" s="2">
-        <v>1</v>
+        <v>-56</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M4" s="2">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="N4" s="2">
-        <v>6</v>
+        <v>-27</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>22</v>
@@ -807,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="Q4" s="2">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="R4" s="2">
-        <v>235</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -821,7 +812,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>20</v>
@@ -830,43 +821,43 @@
         <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="J5" s="2">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="K5" s="2">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M5" s="2">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="N5" s="2">
-        <v>-60</v>
+        <v>22</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P5" s="2">
         <v>1</v>
       </c>
       <c r="Q5" s="2">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="R5" s="2">
-        <v>250</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -877,7 +868,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>20</v>
@@ -886,31 +877,31 @@
         <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J6" s="2">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K6" s="2">
-        <v>-60</v>
+        <v>22</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M6" s="2">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="N6" s="2">
-        <v>-56</v>
+        <v>22</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>22</v>
@@ -919,10 +910,10 @@
         <v>1</v>
       </c>
       <c r="Q6" s="2">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="R6" s="2">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -933,40 +924,40 @@
         <v>19</v>
       </c>
       <c r="C7" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>25</v>
       </c>
       <c r="J7" s="2">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="K7" s="2">
-        <v>-56</v>
+        <v>22</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M7" s="2">
-        <v>41</v>
+        <v>-47</v>
       </c>
       <c r="N7" s="2">
-        <v>-27</v>
+        <v>5</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>22</v>
@@ -975,10 +966,10 @@
         <v>1</v>
       </c>
       <c r="Q7" s="2">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="R7" s="2">
-        <v>268</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -998,215 +989,47 @@
         <v>21</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="J8" s="2">
-        <v>41</v>
+        <v>-47</v>
       </c>
       <c r="K8" s="2">
-        <v>-27</v>
+        <v>5</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="M8" s="2">
-        <v>19</v>
+        <v>-80</v>
       </c>
       <c r="N8" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P8" s="2">
         <v>1</v>
       </c>
       <c r="Q8" s="2">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="R8" s="2">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="2">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="2">
-        <v>19</v>
-      </c>
-      <c r="K9" s="2">
-        <v>22</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="2">
-        <v>7</v>
-      </c>
-      <c r="N9" s="2">
-        <v>22</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="P9" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>277</v>
-      </c>
-      <c r="R9" s="2">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="2">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="2">
-        <v>7</v>
-      </c>
-      <c r="K10" s="2">
-        <v>22</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="2">
-        <v>-47</v>
-      </c>
-      <c r="N10" s="2">
-        <v>5</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="P10" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>279</v>
-      </c>
-      <c r="R10" s="2">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="2">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J11" s="2">
-        <v>-47</v>
-      </c>
-      <c r="K11" s="2">
-        <v>5</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" s="2">
-        <v>-80</v>
-      </c>
-      <c r="N11" s="2">
-        <v>0</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P11" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>285</v>
-      </c>
-      <c r="R11" s="2">
         <v>314</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R563" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R525" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <extLst>
